--- a/tests/fixtures/data/uploadedfiles/tile_excel_test.xlsx
+++ b/tests/fixtures/data/uploadedfiles/tile_excel_test.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johnathanclementi/Documents/Arches/Projects/rdm/arches/tests/fixtures/data/uploadedfiles/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2F2A22-8E0B-7F48-B31A-36371DE44391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="32000" windowHeight="18400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="name" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="geometry" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="creation_date" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="sensitive_information" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="name" sheetId="1" r:id="rId1"/>
+    <sheet name="geometry" sheetId="2" r:id="rId2"/>
+    <sheet name="creation_date" sheetId="3" r:id="rId3"/>
+    <sheet name="sensitive_information" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -23,112 +28,100 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
-  <si>
-    <t xml:space="preserve">tileid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parenttile_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resourceinstance_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sortorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">provisionaledits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nodegroup_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ddef90e7-cc08-4e74-a97e-9e895a486606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d5b977be-fcad-4082-9dd1-bc40637d83f4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c9b37b7c-17b3-11eb-a708-acde48001122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geometry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c2c85d95-f48f-43b9-bc0c-8e23a9d3ed51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEOMETRYCOLLECTION (POINT (-121.95875001707017 36.97531317484881))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c9b37f96-17b3-11eb-a708-acde48001122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819bfd4b-fb21-4d15-bfb8-ac2ad17e569f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c9b38568-17b3-11eb-a708-acde48001122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sensitive_information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a401790f-1721-4bcc-907f-b15cd2b01fc0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c9b38aea-17b3-11eb-a708-acde48001122</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
+  <si>
+    <t>tileid</t>
+  </si>
+  <si>
+    <t>parenttile_id</t>
+  </si>
+  <si>
+    <t>resourceinstance_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>sortorder</t>
+  </si>
+  <si>
+    <t>provisionaledits</t>
+  </si>
+  <si>
+    <t>nodegroup_id</t>
+  </si>
+  <si>
+    <t>ddef90e7-cc08-4e74-a97e-9e895a486606</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>d5b977be-fcad-4082-9dd1-bc40637d83f4</t>
+  </si>
+  <si>
+    <t>Test 1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>c9b37b7c-17b3-11eb-a708-acde48001122</t>
+  </si>
+  <si>
+    <t>geometry</t>
+  </si>
+  <si>
+    <t>c2c85d95-f48f-43b9-bc0c-8e23a9d3ed51</t>
+  </si>
+  <si>
+    <t>GEOMETRYCOLLECTION (POINT (-121.95875001707017 36.97531317484881))</t>
+  </si>
+  <si>
+    <t>c9b37f96-17b3-11eb-a708-acde48001122</t>
+  </si>
+  <si>
+    <t>creation_date</t>
+  </si>
+  <si>
+    <t>819bfd4b-fb21-4d15-bfb8-ac2ad17e569f</t>
+  </si>
+  <si>
+    <t>2024-10-15</t>
+  </si>
+  <si>
+    <t>c9b38568-17b3-11eb-a708-acde48001122</t>
+  </si>
+  <si>
+    <t>sensitive_information</t>
+  </si>
+  <si>
+    <t>a401790f-1721-4bcc-907f-b15cd2b01fc0</t>
+  </si>
+  <si>
+    <t>Test 2</t>
+  </si>
+  <si>
+    <t>c9b38aea-17b3-11eb-a708-acde48001122</t>
+  </si>
+  <si>
+    <t>8e084223-f4f1-4780-b518-f77a6cede269</t>
+  </si>
+  <si>
+    <t>455f8407-8e76-4440-9f57-9e2fe311a208</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -140,7 +133,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -148,84 +141,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -233,12 +207,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -267,7 +241,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -288,7 +262,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -339,7 +313,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -357,258 +331,275 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="8" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
     </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>